--- a/plate3d/PLATE3D_NODE.xlsx
+++ b/plate3d/PLATE3D_NODE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="120">
   <si>
     <t>Bolted four-way beam node - one arm, turned four ways</t>
   </si>
@@ -344,6 +344,30 @@
   </si>
   <si>
     <t>as.core</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>NODE - ISOMETRIC</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>PLATES</t>
+  </si>
+  <si>
+    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -740,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -920,6 +944,7 @@
         <v>34</v>
       </c>
     </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
@@ -1000,6 +1025,7 @@
         <v>60</v>
       </c>
     </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>15</v>
@@ -1040,6 +1066,7 @@
         <v>100</v>
       </c>
     </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
@@ -1128,6 +1155,7 @@
         <v>11</v>
       </c>
     </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>15</v>
@@ -1429,6 +1457,7 @@
         <v>28</v>
       </c>
     </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>15</v>
@@ -1652,6 +1681,7 @@
         <v>76</v>
       </c>
     </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>78</v>
@@ -2065,6 +2095,7 @@
         <v>73</v>
       </c>
     </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>15</v>
@@ -2161,6 +2192,7 @@
         <v>3</v>
       </c>
     </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>15</v>
@@ -2187,16 +2219,67 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" s="3" t="s">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
         <v>111</v>
+      </c>
+      <c r="C59" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59" t="s">
+        <v>112</v>
+      </c>
+      <c r="G59">
+        <v>50</v>
+      </c>
+      <c r="H59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" t="s">
+        <v>115</v>
+      </c>
+      <c r="D60" t="s">
+        <v>116</v>
+      </c>
+      <c r="E60">
+        <v>10</v>
+      </c>
+      <c r="F60" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>114</v>
+      </c>
+      <c r="C61" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" t="s">
+        <v>116</v>
+      </c>
+      <c r="E61">
+        <v>20</v>
+      </c>
+      <c r="F61" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_NODE.xlsx
+++ b/plate3d/PLATE3D_NODE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="112">
   <si>
     <t>Bolted four-way beam node - one arm, turned four ways</t>
   </si>
@@ -344,30 +344,6 @@
   </si>
   <si>
     <t>as.core</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>ISO</t>
-  </si>
-  <si>
-    <t>NODE - ISOMETRIC</t>
-  </si>
-  <si>
-    <t>PLOT</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>PLATES</t>
-  </si>
-  <si>
-    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -764,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -944,7 +920,6 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
@@ -1025,7 +1000,6 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>15</v>
@@ -1066,7 +1040,6 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
@@ -1155,7 +1128,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>15</v>
@@ -1457,7 +1429,6 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>15</v>
@@ -1681,7 +1652,6 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>78</v>
@@ -2095,7 +2065,6 @@
         <v>73</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>15</v>
@@ -2192,7 +2161,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>15</v>
@@ -2219,67 +2187,16 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C59" t="s">
-        <v>106</v>
-      </c>
-      <c r="D59" t="s">
-        <v>112</v>
-      </c>
-      <c r="G59">
-        <v>50</v>
-      </c>
-      <c r="H59" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
-        <v>114</v>
-      </c>
-      <c r="C60" t="s">
-        <v>115</v>
-      </c>
-      <c r="D60" t="s">
-        <v>116</v>
-      </c>
-      <c r="E60">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
-        <v>114</v>
-      </c>
-      <c r="C61" t="s">
-        <v>44</v>
-      </c>
-      <c r="D61" t="s">
-        <v>116</v>
-      </c>
-      <c r="E61">
-        <v>20</v>
-      </c>
-      <c r="F61" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>